--- a/artfynd/A 30780-2024 artfynd.xlsx
+++ b/artfynd/A 30780-2024 artfynd.xlsx
@@ -4235,7 +4235,7 @@
         <v>119839508</v>
       </c>
       <c r="B35" t="n">
-        <v>102825</v>
+        <v>102848</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>119839509</v>
       </c>
       <c r="B36" t="n">
-        <v>91494</v>
+        <v>91512</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 30780-2024 artfynd.xlsx
+++ b/artfynd/A 30780-2024 artfynd.xlsx
@@ -4232,10 +4232,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119839508</v>
+        <v>119839509</v>
       </c>
       <c r="B35" t="n">
-        <v>102848</v>
+        <v>91512</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4248,21 +4248,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222002</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4334,10 +4334,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119839509</v>
+        <v>119839508</v>
       </c>
       <c r="B36" t="n">
-        <v>91512</v>
+        <v>102848</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4350,21 +4350,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
+        <v>222002</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>

--- a/artfynd/A 30780-2024 artfynd.xlsx
+++ b/artfynd/A 30780-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97365676</v>
+        <v>110241832</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547283.0340748661</v>
+        <v>547147</v>
       </c>
       <c r="R2" t="n">
-        <v>6960497.628749822</v>
+        <v>6960299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,40 +756,30 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97365666</v>
+        <v>120663965</v>
       </c>
       <c r="B3" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,34 +787,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547233.1467970689</v>
+        <v>547241</v>
       </c>
       <c r="R3" t="n">
-        <v>6960234.935593624</v>
+        <v>6960305</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,22 +853,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,75 +867,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97365664</v>
+        <v>120663947</v>
       </c>
       <c r="B4" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547127.8156024881</v>
+        <v>546975</v>
       </c>
       <c r="R4" t="n">
-        <v>6960415.711072329</v>
+        <v>6960343</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +951,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,66 +971,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97365669</v>
+        <v>110241830</v>
       </c>
       <c r="B5" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547302.1764064621</v>
+        <v>547209</v>
       </c>
       <c r="R5" t="n">
-        <v>6960474.088823761</v>
+        <v>6960230</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,22 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,31 +1068,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97365659</v>
+        <v>97365673</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,34 +1095,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547146.8597303537</v>
+        <v>547288</v>
       </c>
       <c r="R6" t="n">
-        <v>6960366.978365364</v>
+        <v>6960498</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,19 +1152,9 @@
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,37 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97365660</v>
+        <v>97365666</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547247.9338121859</v>
+        <v>547234</v>
       </c>
       <c r="R7" t="n">
-        <v>6960323.086403624</v>
+        <v>6960235</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1253,9 @@
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,53 +1286,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97365673</v>
+        <v>120663943</v>
       </c>
       <c r="B8" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547288.0779477569</v>
+        <v>547013</v>
       </c>
       <c r="R8" t="n">
-        <v>6960497.70126655</v>
+        <v>6960379</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,22 +1351,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,69 +1371,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97365670</v>
+        <v>120663930</v>
       </c>
       <c r="B9" t="n">
-        <v>86196</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4405</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547463.454468612</v>
+        <v>547235</v>
       </c>
       <c r="R9" t="n">
-        <v>6960548.77333955</v>
+        <v>6960407</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,22 +1448,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,31 +1468,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97365665</v>
+        <v>120663955</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,37 +1491,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547135.1523262652</v>
+        <v>547067</v>
       </c>
       <c r="R10" t="n">
-        <v>6960415.816206821</v>
+        <v>6960367</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1678,22 +1545,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,31 +1565,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110241833</v>
+        <v>119033444</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,34 +1588,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547146.4554900264</v>
+        <v>547073</v>
       </c>
       <c r="R11" t="n">
-        <v>6960299.187867809</v>
+        <v>6960371</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,22 +1642,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,69 +1662,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110241832</v>
+        <v>120663918</v>
       </c>
       <c r="B12" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>504</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547146.4554900264</v>
+        <v>547421</v>
       </c>
       <c r="R12" t="n">
-        <v>6960299.187867809</v>
+        <v>6960561</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,22 +1739,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,69 +1759,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110241831</v>
+        <v>120663924</v>
       </c>
       <c r="B13" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547226.6772612273</v>
+        <v>547327</v>
       </c>
       <c r="R13" t="n">
-        <v>6960429.952917129</v>
+        <v>6960493</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2026,22 +1836,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,31 +1856,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110241834</v>
+        <v>97365671</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,34 +1879,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547310.1396480405</v>
+        <v>547432</v>
       </c>
       <c r="R14" t="n">
-        <v>6960334.97270945</v>
+        <v>6960555</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,22 +1933,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,17 +1953,17 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
     </row>
@@ -2191,16 +1972,11 @@
         <v>119033438</v>
       </c>
       <c r="B15" t="n">
-        <v>91822</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2290,53 +2066,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119033428</v>
+        <v>120663941</v>
       </c>
       <c r="B16" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547327</v>
+        <v>547040</v>
       </c>
       <c r="R16" t="n">
-        <v>6960407</v>
+        <v>6960443</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2360,12 +2131,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,65 +2151,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119033423</v>
+        <v>120663970</v>
       </c>
       <c r="B17" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547294</v>
+        <v>547291</v>
       </c>
       <c r="R17" t="n">
-        <v>6960332</v>
+        <v>6960350</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2462,12 +2228,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,27 +2248,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119033396</v>
+        <v>120663926</v>
       </c>
       <c r="B18" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2510,37 +2271,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547239</v>
+        <v>547258</v>
       </c>
       <c r="R18" t="n">
-        <v>6960219</v>
+        <v>6960467</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2564,12 +2325,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,62 +2345,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119033432</v>
+        <v>97365670</v>
       </c>
       <c r="B19" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547259</v>
+        <v>547463</v>
       </c>
       <c r="R19" t="n">
-        <v>6960273</v>
+        <v>6960549</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2666,12 +2422,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,65 +2442,64 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119033420</v>
+        <v>120663932</v>
       </c>
       <c r="B20" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547240</v>
+        <v>547232</v>
       </c>
       <c r="R20" t="n">
-        <v>6960249</v>
+        <v>6960401</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2768,12 +2523,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2788,27 +2543,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119033397</v>
+        <v>120663951</v>
       </c>
       <c r="B21" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2816,37 +2566,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>4412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547276</v>
+        <v>546994</v>
       </c>
       <c r="R21" t="n">
-        <v>6960411</v>
+        <v>6960320</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2870,12 +2620,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,65 +2640,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119033429</v>
+        <v>119839509</v>
       </c>
       <c r="B22" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547344</v>
+        <v>547457</v>
       </c>
       <c r="R22" t="n">
-        <v>6960422</v>
+        <v>6960559</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2972,12 +2717,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,65 +2737,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119033430</v>
+        <v>120663957</v>
       </c>
       <c r="B23" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547371</v>
+        <v>547107</v>
       </c>
       <c r="R23" t="n">
-        <v>6960445</v>
+        <v>6960355</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3074,12 +2814,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3094,65 +2834,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119033404</v>
+        <v>120663981</v>
       </c>
       <c r="B24" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547107</v>
+        <v>547458</v>
       </c>
       <c r="R24" t="n">
-        <v>6960385</v>
+        <v>6960531</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3176,12 +2911,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3196,62 +2931,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119033389</v>
+        <v>97365659</v>
       </c>
       <c r="B25" t="n">
-        <v>91866</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547081</v>
+        <v>547146</v>
       </c>
       <c r="R25" t="n">
-        <v>6960377</v>
+        <v>6960367</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3278,12 +3008,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3298,27 +3028,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119033422</v>
+        <v>119033432</v>
       </c>
       <c r="B26" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3326,21 +3055,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3350,10 +3079,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547274</v>
+        <v>547259</v>
       </c>
       <c r="R26" t="n">
-        <v>6960298</v>
+        <v>6960273</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3412,15 +3141,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119033425</v>
+        <v>120663963</v>
       </c>
       <c r="B27" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,37 +3152,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547284</v>
+        <v>547247</v>
       </c>
       <c r="R27" t="n">
-        <v>6960352</v>
+        <v>6960274</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3482,12 +3206,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,27 +3226,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119033426</v>
+        <v>120663979</v>
       </c>
       <c r="B28" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3530,37 +3249,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547251</v>
+        <v>547450</v>
       </c>
       <c r="R28" t="n">
-        <v>6960371</v>
+        <v>6960522</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3584,12 +3303,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3604,62 +3323,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119033427</v>
+        <v>110241831</v>
       </c>
       <c r="B29" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547242</v>
+        <v>547227</v>
       </c>
       <c r="R29" t="n">
-        <v>6960411</v>
+        <v>6960430</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,12 +3400,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3706,27 +3420,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119033444</v>
+        <v>97365658</v>
       </c>
       <c r="B30" t="n">
-        <v>91816</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3734,34 +3447,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547073</v>
+        <v>547215</v>
       </c>
       <c r="R30" t="n">
-        <v>6960371</v>
+        <v>6960206</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3788,12 +3501,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3808,62 +3521,61 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119033424</v>
+        <v>97365660</v>
       </c>
       <c r="B31" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>547289</v>
+        <v>547248</v>
       </c>
       <c r="R31" t="n">
-        <v>6960344</v>
+        <v>6960323</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,12 +3602,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3910,62 +3622,61 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119033421</v>
+        <v>97365665</v>
       </c>
       <c r="B32" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547253</v>
+        <v>547135</v>
       </c>
       <c r="R32" t="n">
-        <v>6960275</v>
+        <v>6960416</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3992,12 +3703,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,62 +3723,61 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119033431</v>
+        <v>97365676</v>
       </c>
       <c r="B33" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547355</v>
+        <v>547283</v>
       </c>
       <c r="R33" t="n">
-        <v>6960447</v>
+        <v>6960498</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4094,12 +3804,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4110,31 +3820,35 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119033765</v>
+        <v>110241833</v>
       </c>
       <c r="B34" t="n">
-        <v>90040</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4142,37 +3856,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5734</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Druvfingersvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria botrytis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bourdot</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547143</v>
+        <v>547147</v>
       </c>
       <c r="R34" t="n">
-        <v>6960478</v>
+        <v>6960299</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4199,12 +3910,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,72 +3924,70 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119839509</v>
+        <v>110241834</v>
       </c>
       <c r="B35" t="n">
-        <v>91512</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547457</v>
+        <v>547310</v>
       </c>
       <c r="R35" t="n">
-        <v>6960559</v>
+        <v>6960335</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4302,12 +4011,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4322,65 +4031,64 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119839508</v>
+        <v>119033396</v>
       </c>
       <c r="B36" t="n">
-        <v>102848</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222002</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547457</v>
+        <v>547239</v>
       </c>
       <c r="R36" t="n">
-        <v>6960559</v>
+        <v>6960219</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4404,12 +4112,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4424,65 +4132,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120663943</v>
+        <v>119033397</v>
       </c>
       <c r="B37" t="n">
-        <v>90450</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3215</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547013</v>
+        <v>547276</v>
       </c>
       <c r="R37" t="n">
-        <v>6960379</v>
+        <v>6960411</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4506,12 +4209,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4526,49 +4229,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120663967</v>
+        <v>120663949</v>
       </c>
       <c r="B38" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4578,10 +4276,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>547287</v>
+        <v>546978</v>
       </c>
       <c r="R38" t="n">
-        <v>6960343</v>
+        <v>6960321</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4614,6 +4312,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska födosökshack på klen gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4640,15 +4343,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120663937</v>
+        <v>120663953</v>
       </c>
       <c r="B39" t="n">
-        <v>103570</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4656,21 +4354,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222412</v>
+        <v>106554</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4680,10 +4378,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>547132</v>
+        <v>547001</v>
       </c>
       <c r="R39" t="n">
-        <v>6960452</v>
+        <v>6960317</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4718,12 +4416,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4742,53 +4446,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120663979</v>
+        <v>97365669</v>
       </c>
       <c r="B40" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547450</v>
+        <v>547303</v>
       </c>
       <c r="R40" t="n">
-        <v>6960522</v>
+        <v>6960474</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4812,12 +4511,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4832,65 +4531,64 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120663932</v>
+        <v>119033404</v>
       </c>
       <c r="B41" t="n">
-        <v>88529</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>547232</v>
+        <v>547107</v>
       </c>
       <c r="R41" t="n">
-        <v>6960401</v>
+        <v>6960385</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4914,12 +4612,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4934,65 +4632,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120663963</v>
+        <v>119033419</v>
       </c>
       <c r="B42" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547247</v>
+        <v>547233</v>
       </c>
       <c r="R42" t="n">
-        <v>6960274</v>
+        <v>6960212</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5016,12 +4709,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5036,65 +4729,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120663926</v>
+        <v>119033420</v>
       </c>
       <c r="B43" t="n">
-        <v>91967</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547258</v>
+        <v>547240</v>
       </c>
       <c r="R43" t="n">
-        <v>6960467</v>
+        <v>6960249</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5118,12 +4806,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5138,65 +4826,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120663951</v>
+        <v>119033421</v>
       </c>
       <c r="B44" t="n">
-        <v>88529</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546994</v>
+        <v>547253</v>
       </c>
       <c r="R44" t="n">
-        <v>6960320</v>
+        <v>6960275</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5220,12 +4903,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5240,65 +4923,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120663955</v>
+        <v>119033422</v>
       </c>
       <c r="B45" t="n">
-        <v>91947</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547067</v>
+        <v>547274</v>
       </c>
       <c r="R45" t="n">
-        <v>6960367</v>
+        <v>6960298</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5322,12 +5000,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5342,27 +5020,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120663935</v>
+        <v>119033423</v>
       </c>
       <c r="B46" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5390,17 +5063,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>547156</v>
+        <v>547294</v>
       </c>
       <c r="R46" t="n">
-        <v>6960361</v>
+        <v>6960332</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5424,12 +5097,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5444,65 +5117,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120663928</v>
+        <v>119033424</v>
       </c>
       <c r="B47" t="n">
-        <v>91983</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547252</v>
+        <v>547289</v>
       </c>
       <c r="R47" t="n">
-        <v>6960437</v>
+        <v>6960344</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5526,12 +5194,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5546,65 +5214,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120663957</v>
+        <v>119033425</v>
       </c>
       <c r="B48" t="n">
-        <v>91612</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547107</v>
+        <v>547284</v>
       </c>
       <c r="R48" t="n">
-        <v>6960355</v>
+        <v>6960352</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5628,12 +5291,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5648,65 +5311,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120663930</v>
+        <v>119033426</v>
       </c>
       <c r="B49" t="n">
-        <v>91947</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547235</v>
+        <v>547251</v>
       </c>
       <c r="R49" t="n">
-        <v>6960407</v>
+        <v>6960371</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5730,12 +5388,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5750,27 +5408,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120663975</v>
+        <v>119033427</v>
       </c>
       <c r="B50" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5798,17 +5451,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547405</v>
+        <v>547242</v>
       </c>
       <c r="R50" t="n">
-        <v>6960470</v>
+        <v>6960411</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5832,12 +5485,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5852,65 +5505,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120663924</v>
+        <v>119033428</v>
       </c>
       <c r="B51" t="n">
-        <v>91949</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
         <v>547327</v>
       </c>
       <c r="R51" t="n">
-        <v>6960493</v>
+        <v>6960407</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5934,12 +5582,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5954,65 +5602,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120663953</v>
+        <v>119033429</v>
       </c>
       <c r="B52" t="n">
-        <v>8421</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547001</v>
+        <v>547344</v>
       </c>
       <c r="R52" t="n">
-        <v>6960317</v>
+        <v>6960422</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6036,17 +5679,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6055,72 +5693,66 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120663947</v>
+        <v>119033430</v>
       </c>
       <c r="B53" t="n">
-        <v>88012</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>546975</v>
+        <v>547371</v>
       </c>
       <c r="R53" t="n">
-        <v>6960343</v>
+        <v>6960445</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6144,12 +5776,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6164,65 +5796,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120663941</v>
+        <v>119033431</v>
       </c>
       <c r="B54" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>norrkrången, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547040</v>
+        <v>547355</v>
       </c>
       <c r="R54" t="n">
-        <v>6960443</v>
+        <v>6960447</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6246,12 +5873,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6266,49 +5893,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120663970</v>
+        <v>120663935</v>
       </c>
       <c r="B55" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6318,10 +5940,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547291</v>
+        <v>547156</v>
       </c>
       <c r="R55" t="n">
-        <v>6960350</v>
+        <v>6960361</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6380,37 +6002,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120663981</v>
+        <v>120663967</v>
       </c>
       <c r="B56" t="n">
-        <v>91612</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6420,10 +6037,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547458</v>
+        <v>547287</v>
       </c>
       <c r="R56" t="n">
-        <v>6960531</v>
+        <v>6960343</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6482,37 +6099,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120663949</v>
+        <v>120663975</v>
       </c>
       <c r="B57" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6522,10 +6134,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>546978</v>
+        <v>547405</v>
       </c>
       <c r="R57" t="n">
-        <v>6960321</v>
+        <v>6960470</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6560,11 +6172,6 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska födosökshack på klen gran</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6586,6 +6193,402 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>97365664</v>
+      </c>
+      <c r="B58" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>547128</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6960416</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>119839508</v>
+      </c>
+      <c r="B59" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>547457</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6960559</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120663937</v>
+      </c>
+      <c r="B60" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>547132</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6960452</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>110241828</v>
+      </c>
+      <c r="B61" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>547229</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6960318</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30780-2024 artfynd.xlsx
+++ b/artfynd/A 30780-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110241832</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663965</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663947</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110241830</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365673</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365666</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663943</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663930</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1574,6 +1619,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663955</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1671,6 +1721,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033444</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1768,6 +1823,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663918</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1865,6 +1925,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663924</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1966,6 +2031,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365671</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2063,6 +2133,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033438</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2160,6 +2235,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663941</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2257,6 +2337,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663970</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2354,6 +2439,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663926</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2455,6 +2545,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365670</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2552,6 +2647,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663932</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2649,6 +2749,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663951</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2746,6 +2851,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839509</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2843,6 +2953,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663957</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2940,6 +3055,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663981</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3041,6 +3161,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365659</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3138,6 +3263,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033432</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3235,6 +3365,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663963</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3332,6 +3467,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663979</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3433,6 +3573,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110241831</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3534,6 +3679,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365658</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3635,6 +3785,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365660</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3736,6 +3891,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365665</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3842,6 +4002,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365676</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3943,6 +4108,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110241833</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4044,6 +4214,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110241834</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4141,6 +4316,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033396</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4238,6 +4418,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033397</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4340,6 +4525,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663949</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4443,6 +4633,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663953</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4544,6 +4739,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365669</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4641,6 +4841,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033404</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4738,6 +4943,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033419</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4835,6 +5045,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033420</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4932,6 +5147,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033421</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5029,6 +5249,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033422</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5126,6 +5351,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033423</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5223,6 +5453,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033424</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5320,6 +5555,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033425</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5417,6 +5657,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033426</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5514,6 +5759,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033427</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5611,6 +5861,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033428</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5708,6 +5963,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033429</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5805,6 +6065,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033430</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5902,6 +6167,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033431</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5999,6 +6269,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663935</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6096,6 +6371,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663967</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6193,6 +6473,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663975</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6294,6 +6579,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365664</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6391,6 +6681,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839508</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6488,6 +6783,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663937</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6589,8 +6889,75 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110241828</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>